--- a/RiscISAv1.0.xlsx
+++ b/RiscISAv1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC08F8B-34B3-4168-960C-2A01FD70FDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DEBCB1-8026-4508-BF49-C74DB83D4644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="489" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="422">
   <si>
     <t>bit0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,10 +374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>barim</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目标寄存器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1077,10 +1073,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>jmp, ret</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>divu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1141,10 +1133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FCSR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>divs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1197,14 +1185,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>makei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>makeh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>op0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1533,7 +1513,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>raddri</t>
+    <t>jmp/ret</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPSR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPSR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPSR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loadi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shldi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loadf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fd 0-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fs 0-15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1541,7 +1561,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1576,6 +1596,14 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1641,7 +1669,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1861,11 +1889,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1985,11 +2062,39 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2728,10 +2833,10 @@
         <v>65</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>64</v>
@@ -2882,16 +2987,16 @@
         <v>66</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P25" s="12" t="s">
         <v>65</v>
@@ -3150,16 +3255,16 @@
       <c r="Q32" s="12"/>
       <c r="R32" s="12"/>
       <c r="S32" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W32" s="12" t="s">
         <v>66</v>
@@ -3486,16 +3591,16 @@
       <c r="X39" s="12"/>
       <c r="Y39" s="12"/>
       <c r="Z39" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AA39" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AB39" s="12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AC39" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AD39" s="12" t="s">
         <v>67</v>
@@ -3713,7 +3818,7 @@
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="F45" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>78</v>
@@ -4017,7 +4122,7 @@
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.2">
       <c r="F51" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>78</v>
@@ -4361,7 +4466,7 @@
     </row>
     <row r="58" spans="2:33" x14ac:dyDescent="0.2">
       <c r="F58" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>78</v>
@@ -4667,7 +4772,7 @@
     </row>
     <row r="65" spans="6:33" x14ac:dyDescent="0.2">
       <c r="F65" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>78</v>
@@ -4709,809 +4814,827 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5089180-8837-4051-A495-79C0A9223B45}">
-  <dimension ref="B2:P43"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:P45"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="63"/>
+    <col min="2" max="2" width="11" style="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.75" style="63"/>
+    <col min="6" max="6" width="12.875" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="63" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" style="63"/>
+    <col min="9" max="9" width="11" style="63" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.75" style="63"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="B2" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="63" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B3" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D4" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B5" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" s="64" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B6" s="63" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="63" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>224</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B9" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B12" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>277</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>347</v>
+      </c>
+      <c r="J13" s="64" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="K13" s="64" t="s">
+        <v>352</v>
+      </c>
+      <c r="L13" s="64" t="s">
+        <v>353</v>
+      </c>
+      <c r="M13" s="64" t="s">
+        <v>354</v>
+      </c>
+      <c r="N13" s="64" t="s">
+        <v>355</v>
+      </c>
+      <c r="O13" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="P13" s="64" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B14" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>278</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>348</v>
+      </c>
+      <c r="J14" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="K14" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="L14" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="M14" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="N14" s="64" t="s">
+        <v>362</v>
+      </c>
+      <c r="O14" s="64" t="s">
+        <v>363</v>
+      </c>
+      <c r="P14" s="64" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B15" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>349</v>
+      </c>
+      <c r="J15" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="K15" s="64" t="s">
+        <v>366</v>
+      </c>
+      <c r="L15" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="M15" s="64" t="s">
+        <v>369</v>
+      </c>
+      <c r="N15" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="O15" s="64" t="s">
+        <v>371</v>
+      </c>
+      <c r="P15" s="64" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>350</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>373</v>
+      </c>
+      <c r="K16" s="64" t="s">
+        <v>374</v>
+      </c>
+      <c r="L16" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="M16" s="64" t="s">
+        <v>375</v>
+      </c>
+      <c r="N16" s="64" t="s">
+        <v>376</v>
+      </c>
+      <c r="O16" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="P16" s="64" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="63" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>305</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="G19" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="I21" s="64" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B26" s="63" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="E28" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="G28" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="64" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="E29" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="G29" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B30" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" s="63" t="s">
         <v>328</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G30" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="I30" s="64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B31" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E31" s="63" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" s="63" t="s">
         <v>329</v>
       </c>
-      <c r="F3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G31" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="I31" s="64" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B32" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="63" t="s">
         <v>330</v>
       </c>
-      <c r="G4" t="s">
-        <v>213</v>
-      </c>
-      <c r="I4" s="54" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" t="s">
-        <v>214</v>
-      </c>
-      <c r="I5" s="54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I6" s="54" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G32" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="I32" s="64" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B33" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" s="63" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="G33" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="I33" s="64" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B34" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="G7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I7" s="54" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" t="s">
-        <v>222</v>
-      </c>
-      <c r="F8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G8" t="s">
-        <v>219</v>
-      </c>
-      <c r="I8" s="54" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" t="s">
-        <v>223</v>
-      </c>
-      <c r="F9" t="s">
-        <v>226</v>
-      </c>
-      <c r="G9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I9" s="54" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" t="s">
-        <v>209</v>
-      </c>
-      <c r="I10" s="54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" t="s">
-        <v>199</v>
-      </c>
-      <c r="F11" t="s">
-        <v>210</v>
-      </c>
-      <c r="I11" s="54" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" t="s">
-        <v>200</v>
-      </c>
-      <c r="F12" t="s">
-        <v>211</v>
-      </c>
-      <c r="I12" s="54" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G13" t="s">
-        <v>278</v>
-      </c>
-      <c r="I13" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="J13" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="K13" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="L13" s="54" t="s">
-        <v>358</v>
-      </c>
-      <c r="M13" s="54" t="s">
-        <v>359</v>
-      </c>
-      <c r="N13" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="O13" s="54" t="s">
-        <v>361</v>
-      </c>
-      <c r="P13" s="54" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" t="s">
-        <v>217</v>
-      </c>
-      <c r="E14" t="s">
-        <v>203</v>
-      </c>
-      <c r="F14" t="s">
-        <v>227</v>
-      </c>
-      <c r="G14" t="s">
-        <v>279</v>
-      </c>
-      <c r="I14" s="54" t="s">
-        <v>353</v>
-      </c>
-      <c r="J14" s="54" t="s">
-        <v>363</v>
-      </c>
-      <c r="K14" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="L14" s="54" t="s">
-        <v>365</v>
-      </c>
-      <c r="M14" s="54" t="s">
-        <v>366</v>
-      </c>
-      <c r="N14" s="54" t="s">
-        <v>367</v>
-      </c>
-      <c r="O14" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="P14" s="54" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" t="s">
-        <v>228</v>
-      </c>
-      <c r="G15" t="s">
-        <v>280</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="J15" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="K15" s="54" t="s">
-        <v>371</v>
-      </c>
-      <c r="L15" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="M15" s="54" t="s">
-        <v>374</v>
-      </c>
-      <c r="N15" s="54" t="s">
-        <v>375</v>
-      </c>
-      <c r="O15" s="54" t="s">
-        <v>376</v>
-      </c>
-      <c r="P15" s="54" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" t="s">
-        <v>205</v>
-      </c>
-      <c r="F16" t="s">
-        <v>283</v>
-      </c>
-      <c r="G16" t="s">
-        <v>281</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>355</v>
-      </c>
-      <c r="J16" s="54" t="s">
-        <v>378</v>
-      </c>
-      <c r="K16" s="54" t="s">
+      <c r="I34" s="64" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B35" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="D35" s="63" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="I35" s="64" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B36" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="I36" s="64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B37" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="F37" s="63" t="s">
+        <v>334</v>
+      </c>
+      <c r="G37" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>407</v>
+      </c>
+      <c r="J37" s="65" t="s">
         <v>379</v>
       </c>
-      <c r="L16" s="54" t="s">
-        <v>372</v>
-      </c>
-      <c r="M16" s="54" t="s">
+      <c r="K37" s="65" t="s">
+        <v>383</v>
+      </c>
+      <c r="L37" s="65" t="s">
+        <v>384</v>
+      </c>
+      <c r="M37" s="65" t="s">
+        <v>385</v>
+      </c>
+      <c r="N37" s="65" t="s">
+        <v>386</v>
+      </c>
+      <c r="O37" s="65" t="s">
+        <v>387</v>
+      </c>
+      <c r="P37" s="65" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B38" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="E38" s="63" t="s">
+        <v>266</v>
+      </c>
+      <c r="F38" s="63" t="s">
+        <v>335</v>
+      </c>
+      <c r="G38" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>408</v>
+      </c>
+      <c r="J38" s="65" t="s">
         <v>380</v>
       </c>
-      <c r="N16" s="54" t="s">
+      <c r="K38" s="64" t="s">
+        <v>389</v>
+      </c>
+      <c r="L38" s="65" t="s">
+        <v>390</v>
+      </c>
+      <c r="M38" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="N38" s="65" t="s">
+        <v>392</v>
+      </c>
+      <c r="O38" s="64" t="s">
+        <v>393</v>
+      </c>
+      <c r="P38" s="65" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B39" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="E39" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="F39" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="G39" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="I39" s="64" t="s">
+        <v>409</v>
+      </c>
+      <c r="J39" s="65" t="s">
         <v>381</v>
       </c>
-      <c r="O16" s="54" t="s">
+      <c r="K39" s="64" t="s">
+        <v>395</v>
+      </c>
+      <c r="L39" s="65" t="s">
+        <v>396</v>
+      </c>
+      <c r="M39" s="64" t="s">
+        <v>397</v>
+      </c>
+      <c r="N39" s="65" t="s">
+        <v>398</v>
+      </c>
+      <c r="O39" s="64" t="s">
+        <v>399</v>
+      </c>
+      <c r="P39" s="65" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B40" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D40" s="63" t="s">
+        <v>269</v>
+      </c>
+      <c r="E40" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="F40" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="G40" s="63" t="s">
+        <v>276</v>
+      </c>
+      <c r="I40" s="64" t="s">
+        <v>410</v>
+      </c>
+      <c r="J40" s="65" t="s">
         <v>382</v>
       </c>
-      <c r="P16" s="54" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" t="s">
-        <v>284</v>
-      </c>
-      <c r="E17" t="s">
-        <v>188</v>
-      </c>
-      <c r="F17" t="s">
-        <v>285</v>
-      </c>
-      <c r="G17" t="s">
-        <v>229</v>
-      </c>
-      <c r="I17" s="54" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" t="s">
-        <v>288</v>
-      </c>
-      <c r="E18" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" t="s">
-        <v>287</v>
-      </c>
-      <c r="G18" t="s">
-        <v>230</v>
-      </c>
-      <c r="I18" s="54" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D19" t="s">
-        <v>307</v>
-      </c>
-      <c r="F19" t="s">
-        <v>306</v>
-      </c>
-      <c r="G19" t="s">
-        <v>289</v>
-      </c>
-      <c r="I19" s="54" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>328</v>
-      </c>
-      <c r="D25" t="s">
-        <v>329</v>
-      </c>
-      <c r="F25" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>232</v>
-      </c>
-      <c r="D26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" t="s">
-        <v>254</v>
-      </c>
-      <c r="F26" t="s">
-        <v>331</v>
-      </c>
-      <c r="G26" t="s">
-        <v>213</v>
-      </c>
-      <c r="I26" s="54" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>233</v>
-      </c>
-      <c r="D27" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F27" t="s">
-        <v>332</v>
-      </c>
-      <c r="G27" t="s">
-        <v>346</v>
-      </c>
-      <c r="I27" s="54" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>234</v>
-      </c>
-      <c r="D28" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" t="s">
-        <v>256</v>
-      </c>
-      <c r="F28" t="s">
-        <v>333</v>
-      </c>
-      <c r="G28" t="s">
-        <v>347</v>
-      </c>
-      <c r="I28" s="54" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>235</v>
-      </c>
-      <c r="D29" t="s">
-        <v>251</v>
-      </c>
-      <c r="E29" t="s">
-        <v>257</v>
-      </c>
-      <c r="F29" t="s">
-        <v>334</v>
-      </c>
-      <c r="G29" t="s">
-        <v>348</v>
-      </c>
-      <c r="I29" s="54" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D30" t="s">
-        <v>252</v>
-      </c>
-      <c r="E30" t="s">
-        <v>258</v>
-      </c>
-      <c r="F30" t="s">
-        <v>335</v>
-      </c>
-      <c r="G30" t="s">
-        <v>349</v>
-      </c>
-      <c r="I30" s="54" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>237</v>
-      </c>
-      <c r="D31" t="s">
-        <v>253</v>
-      </c>
-      <c r="E31" t="s">
-        <v>259</v>
-      </c>
-      <c r="F31" t="s">
-        <v>336</v>
-      </c>
-      <c r="G31" t="s">
-        <v>350</v>
-      </c>
-      <c r="I31" s="54" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>238</v>
-      </c>
-      <c r="D32" t="s">
-        <v>260</v>
-      </c>
-      <c r="F32" t="s">
-        <v>209</v>
-      </c>
-      <c r="I32" s="54" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>239</v>
-      </c>
-      <c r="D33" t="s">
-        <v>261</v>
-      </c>
-      <c r="F33" t="s">
-        <v>337</v>
-      </c>
-      <c r="I33" s="54" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" t="s">
-        <v>262</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="K40" s="64" t="s">
+        <v>401</v>
+      </c>
+      <c r="L40" s="65" t="s">
+        <v>402</v>
+      </c>
+      <c r="M40" s="64" t="s">
+        <v>403</v>
+      </c>
+      <c r="N40" s="65" t="s">
+        <v>404</v>
+      </c>
+      <c r="O40" s="64" t="s">
+        <v>405</v>
+      </c>
+      <c r="P40" s="65" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B41" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="F41" s="63" t="s">
         <v>338</v>
       </c>
-      <c r="I34" s="54" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" t="s">
-        <v>263</v>
-      </c>
-      <c r="E35" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="I41" s="64" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B42" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="D42" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="F42" s="63" t="s">
         <v>339</v>
       </c>
-      <c r="G35" t="s">
-        <v>274</v>
-      </c>
-      <c r="I35" s="54" t="s">
+      <c r="I42" s="64" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="D43" s="63" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="I43" s="64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B45" s="63" t="s">
         <v>412</v>
       </c>
-      <c r="J35" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="K35" s="55" t="s">
-        <v>388</v>
-      </c>
-      <c r="L35" s="55" t="s">
-        <v>389</v>
-      </c>
-      <c r="M35" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="N35" s="55" t="s">
-        <v>391</v>
-      </c>
-      <c r="O35" s="55" t="s">
-        <v>392</v>
-      </c>
-      <c r="P35" s="55" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>242</v>
-      </c>
-      <c r="D36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" t="s">
-        <v>267</v>
-      </c>
-      <c r="F36" t="s">
-        <v>340</v>
-      </c>
-      <c r="G36" t="s">
-        <v>275</v>
-      </c>
-      <c r="I36" s="54" t="s">
-        <v>413</v>
-      </c>
-      <c r="J36" s="55" t="s">
-        <v>385</v>
-      </c>
-      <c r="K36" s="54" t="s">
-        <v>394</v>
-      </c>
-      <c r="L36" s="55" t="s">
-        <v>395</v>
-      </c>
-      <c r="M36" s="54" t="s">
-        <v>396</v>
-      </c>
-      <c r="N36" s="55" t="s">
-        <v>397</v>
-      </c>
-      <c r="O36" s="54" t="s">
-        <v>398</v>
-      </c>
-      <c r="P36" s="55" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>243</v>
-      </c>
-      <c r="D37" t="s">
-        <v>265</v>
-      </c>
-      <c r="E37" t="s">
-        <v>268</v>
-      </c>
-      <c r="F37" t="s">
-        <v>341</v>
-      </c>
-      <c r="G37" t="s">
-        <v>276</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>414</v>
-      </c>
-      <c r="J37" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="K37" s="54" t="s">
-        <v>400</v>
-      </c>
-      <c r="L37" s="55" t="s">
-        <v>401</v>
-      </c>
-      <c r="M37" s="54" t="s">
-        <v>402</v>
-      </c>
-      <c r="N37" s="55" t="s">
-        <v>403</v>
-      </c>
-      <c r="O37" s="54" t="s">
-        <v>404</v>
-      </c>
-      <c r="P37" s="55" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>244</v>
-      </c>
-      <c r="D38" t="s">
-        <v>270</v>
-      </c>
-      <c r="E38" t="s">
-        <v>269</v>
-      </c>
-      <c r="F38" t="s">
-        <v>342</v>
-      </c>
-      <c r="G38" t="s">
-        <v>277</v>
-      </c>
-      <c r="I38" s="54" t="s">
+      <c r="I45" s="64" t="s">
         <v>415</v>
-      </c>
-      <c r="J38" s="55" t="s">
-        <v>387</v>
-      </c>
-      <c r="K38" s="54" t="s">
-        <v>406</v>
-      </c>
-      <c r="L38" s="55" t="s">
-        <v>407</v>
-      </c>
-      <c r="M38" s="54" t="s">
-        <v>408</v>
-      </c>
-      <c r="N38" s="55" t="s">
-        <v>409</v>
-      </c>
-      <c r="O38" s="54" t="s">
-        <v>410</v>
-      </c>
-      <c r="P38" s="55" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>245</v>
-      </c>
-      <c r="D39" t="s">
-        <v>271</v>
-      </c>
-      <c r="F39" t="s">
-        <v>343</v>
-      </c>
-      <c r="I39" s="54" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>246</v>
-      </c>
-      <c r="D40" t="s">
-        <v>272</v>
-      </c>
-      <c r="F40" t="s">
-        <v>344</v>
-      </c>
-      <c r="I40" s="54" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>247</v>
-      </c>
-      <c r="D41" t="s">
-        <v>273</v>
-      </c>
-      <c r="F41" t="s">
-        <v>345</v>
-      </c>
-      <c r="I41" s="54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -5531,227 +5654,234 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="53" t="s">
+      <c r="B2" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="G2" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="M2" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="N2" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="O2" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="53" t="s">
+      <c r="Q2" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="53" t="s">
+      <c r="S2" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="L2" s="53" t="s">
+      <c r="T2" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="U2" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="M2" s="53" t="s">
+      <c r="V2" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="N2" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="O2" s="53" t="s">
+      <c r="W2" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="X2" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="Q2" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="R2" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="S2" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="T2" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="U2" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="V2" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="W2" s="53" t="s">
-        <v>316</v>
-      </c>
-      <c r="X2" s="53" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="D3" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="53" t="s">
+      <c r="I3" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="60" t="s">
+        <v>314</v>
+      </c>
+      <c r="R3" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="S3" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="T3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="U3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="V3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="W3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="X3" s="62" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="60"/>
+      <c r="C4" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="L3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="53" t="s">
-        <v>317</v>
-      </c>
-      <c r="R3" s="53" t="s">
+      <c r="K4" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="O4" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="S3" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="T3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X3" s="53" t="s">
+      <c r="S4" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="T4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="U4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="X4" s="62" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C4" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="53" t="s">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B5" s="60"/>
+      <c r="C5" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="55"/>
+      <c r="J5" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="K4" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="L4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="R4" s="53" t="s">
+      <c r="K5" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O5" s="56"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="S4" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="T4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W4" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X4" s="53" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C5" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="K5" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L5" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N5" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" s="53" t="s">
-        <v>109</v>
-      </c>
       <c r="S5" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T5" s="53" t="s">
         <v>88</v>
@@ -5765,13 +5895,15 @@
       <c r="W5" s="53" t="s">
         <v>88</v>
       </c>
+      <c r="X5" s="56"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B6" s="55"/>
       <c r="C6" s="53" t="s">
         <v>93</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>88</v>
@@ -5779,167 +5911,183 @@
       <c r="F6" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="53" t="s">
-        <v>94</v>
-      </c>
+      <c r="G6" s="56"/>
+      <c r="I6" s="55"/>
       <c r="J6" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="K6" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="56"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="S6" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W6" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X6" s="56"/>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B7" s="55"/>
+      <c r="G7" s="56"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="K6" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R6" s="53" t="s">
+      <c r="K7" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="56"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="S6" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V6" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W6" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J7" s="53" t="s">
+      <c r="S7" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="56"/>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B8" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>411</v>
+      </c>
+      <c r="I8" s="55"/>
+      <c r="J8" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="K7" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R7" s="53" t="s">
+      <c r="K8" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8" s="56"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="S7" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V7" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W7" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B8" s="53" t="s">
+      <c r="S8" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X8" s="56"/>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B9" s="60"/>
+      <c r="C9" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="J8" s="53" t="s">
+      <c r="D9" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="55"/>
+      <c r="J9" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="K8" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="53" t="s">
+      <c r="K9" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" s="56"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="S8" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V8" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W8" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C9" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="J9" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="K9" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R9" s="53" t="s">
-        <v>113</v>
-      </c>
       <c r="S9" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T9" s="53" t="s">
         <v>88</v>
@@ -5953,8 +6101,10 @@
       <c r="W9" s="53" t="s">
         <v>88</v>
       </c>
+      <c r="X9" s="56"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="55"/>
       <c r="C10" s="53" t="s">
         <v>91</v>
       </c>
@@ -5962,2590 +6112,2863 @@
         <v>88</v>
       </c>
       <c r="E10" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="56"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="53" t="s">
+      <c r="K10" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="56"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X10" s="56"/>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B11" s="57"/>
+      <c r="C11" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="59"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O11" s="56"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X11" s="56"/>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I12" s="55"/>
+      <c r="J12" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O12" s="56"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="S12" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X12" s="56"/>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I13" s="55"/>
+      <c r="J13" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="K13" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O13" s="56"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="S13" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W13" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X13" s="56"/>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I14" s="55"/>
+      <c r="J14" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="56"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="S14" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W14" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X14" s="56"/>
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="55"/>
+      <c r="J15" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="56"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="S15" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W15" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X15" s="56"/>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B16" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="I16" s="55"/>
+      <c r="J16" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O16" s="56"/>
+      <c r="Q16" s="55"/>
+      <c r="R16" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X16" s="56"/>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B17" s="60"/>
+      <c r="C17" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="55"/>
+      <c r="J17" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="K17" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O17" s="56"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="S17" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="T17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="U17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W17" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X17" s="56"/>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B18" s="55"/>
+      <c r="C18" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="56"/>
+      <c r="I18" s="55"/>
+      <c r="O18" s="56"/>
+      <c r="Q18" s="55"/>
+      <c r="X18" s="56"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B19" s="55"/>
+      <c r="C19" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="56"/>
+      <c r="I19" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="L19" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M19" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O19" s="56"/>
+      <c r="Q19" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="R19" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="S19" s="61" t="s">
+        <v>141</v>
+      </c>
+      <c r="T19" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="U19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="V19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="W19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="X19" s="62" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B20" s="55"/>
+      <c r="C20" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="56"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="K20" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M20" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" s="56"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="S20" s="61" t="s">
+        <v>141</v>
+      </c>
+      <c r="T20" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="U20" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="V20" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="W20" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="X20" s="62" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B21" s="55"/>
+      <c r="C21" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="56"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O21" s="56"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="S21" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T21" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W21" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X21" s="56"/>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B22" s="55"/>
+      <c r="C22" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="56"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L22" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" s="56"/>
+      <c r="Q22" s="55"/>
+      <c r="R22" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="S22" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T22" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X22" s="56"/>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="55"/>
+      <c r="C23" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="56"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="K23" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L23" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O23" s="56"/>
+      <c r="Q23" s="55"/>
+      <c r="R23" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="S23" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T23" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W23" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X23" s="56"/>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B24" s="55"/>
+      <c r="C24" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="56"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K24" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O24" s="56"/>
+      <c r="Q24" s="55"/>
+      <c r="R24" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S24" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T24" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W24" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X24" s="56"/>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B25" s="55"/>
+      <c r="C25" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="56"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L25" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O25" s="56"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="S25" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T25" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W25" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X25" s="56"/>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B26" s="55"/>
+      <c r="C26" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="56"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L26" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O26" s="56"/>
+      <c r="Q26" s="55"/>
+      <c r="R26" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S26" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T26" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W26" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X26" s="56"/>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B27" s="55"/>
+      <c r="C27" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="56"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O27" s="56"/>
+      <c r="Q27" s="55"/>
+      <c r="R27" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="S27" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T27" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W27" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X27" s="56"/>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B28" s="55"/>
+      <c r="C28" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="56"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L28" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O28" s="56"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="S28" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T28" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W28" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X28" s="56"/>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B29" s="55"/>
+      <c r="C29" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="56"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L29" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O29" s="56"/>
+      <c r="Q29" s="55"/>
+      <c r="R29" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="S29" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T29" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W29" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X29" s="56"/>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B30" s="55"/>
+      <c r="C30" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="56"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="K30" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O30" s="56"/>
+      <c r="Q30" s="55"/>
+      <c r="R30" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="S30" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T30" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W30" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X30" s="56"/>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B31" s="55"/>
+      <c r="G31" s="56"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="K31" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="N31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O31" s="56"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="S31" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T31" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W31" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X31" s="56"/>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B32" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="56"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="M32" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="N32" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="O32" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="S32" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T32" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U32" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V32" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W32" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X32" s="56"/>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B33" s="55"/>
+      <c r="C33" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="56"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="K33" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="L33" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="M33" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="N33" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="O33" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q33" s="55"/>
+      <c r="R33" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="S33" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="T33" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U33" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="V33" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W33" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X33" s="56"/>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B34" s="55"/>
+      <c r="C34" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" s="53" t="s">
+      <c r="E34" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="56"/>
+      <c r="I34" s="55"/>
+      <c r="O34" s="56"/>
+      <c r="Q34" s="55"/>
+      <c r="X34" s="56"/>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B35" s="55"/>
+      <c r="C35" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="S10" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V10" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W10" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C11" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="53" t="s">
+      <c r="E35" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="56"/>
+      <c r="I35" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="J35" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="L35" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M35" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="N35" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O35" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q35" s="55" t="s">
+        <v>316</v>
+      </c>
+      <c r="R35" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="S35" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="T35" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="U35" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="V35" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W35" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X35" s="56" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B36" s="55"/>
+      <c r="C36" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="56"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="K36" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="L36" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M36" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="N36" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O36" s="56" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="S36" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="T36" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="U36" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="V36" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W36" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X36" s="56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B37" s="55"/>
+      <c r="C37" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="56"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L37" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M37" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N37" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O37" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q37" s="55"/>
+      <c r="R37" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="S37" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T37" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U37" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V37" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W37" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X37" s="56" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B38" s="55"/>
+      <c r="C38" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="56"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L38" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M38" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N38" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O38" s="56" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q38" s="55"/>
+      <c r="R38" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="S38" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T38" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U38" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V38" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W38" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X38" s="56"/>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B39" s="55"/>
+      <c r="C39" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" s="53" t="s">
+      <c r="D39" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="56"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="K39" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L39" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M39" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N39" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O39" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q39" s="55"/>
+      <c r="R39" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="S39" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T39" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U39" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V39" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W39" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X39" s="56" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B40" s="55"/>
+      <c r="C40" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="56"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K40" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L40" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M40" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N40" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O40" s="56" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q40" s="55"/>
+      <c r="R40" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S40" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T40" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U40" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V40" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W40" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X40" s="56" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B41" s="55"/>
+      <c r="C41" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="K11" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" s="53" t="s">
+      <c r="D41" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="56"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="K41" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L41" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M41" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N41" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O41" s="56" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="S41" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T41" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U41" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V41" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W41" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X41" s="56"/>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B42" s="55"/>
+      <c r="C42" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="56"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="K42" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L42" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M42" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N42" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O42" s="56" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q42" s="55"/>
+      <c r="R42" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S42" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T42" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U42" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V42" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W42" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X42" s="56"/>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B43" s="55"/>
+      <c r="C43" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F43" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="56"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K43" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L43" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M43" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N43" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O43" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q43" s="55"/>
+      <c r="R43" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="S43" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T43" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U43" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V43" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W43" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X43" s="56"/>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B44" s="55"/>
+      <c r="C44" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="56"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="S11" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V11" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W11" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J12" s="53" t="s">
+      <c r="K44" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L44" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M44" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N44" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O44" s="56"/>
+      <c r="Q44" s="55"/>
+      <c r="R44" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="S44" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T44" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U44" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V44" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W44" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X44" s="56"/>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B45" s="55"/>
+      <c r="C45" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="56"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="K12" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" s="53" t="s">
+      <c r="K45" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L45" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M45" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N45" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O45" s="56"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="S12" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V12" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W12" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J13" s="53" t="s">
+      <c r="S45" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T45" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U45" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V45" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W45" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X45" s="56"/>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B46" s="55"/>
+      <c r="C46" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="56"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="K13" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="53" t="s">
+      <c r="K46" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L46" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M46" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N46" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O46" s="56"/>
+      <c r="Q46" s="55"/>
+      <c r="R46" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="S13" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V13" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W13" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J14" s="53" t="s">
+      <c r="S46" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T46" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U46" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V46" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W46" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X46" s="56"/>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B47" s="55"/>
+      <c r="G47" s="56"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="K14" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="53" t="s">
+      <c r="K47" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L47" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M47" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N47" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O47" s="56"/>
+      <c r="Q47" s="55"/>
+      <c r="R47" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="S14" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V14" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W14" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B15" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" s="53" t="s">
+      <c r="S47" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T47" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U47" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V47" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W47" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X47" s="56"/>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B48" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="G48" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="I48" s="55"/>
+      <c r="J48" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="K15" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" s="53" t="s">
+      <c r="K48" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L48" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M48" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N48" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O48" s="56"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="S15" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V15" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W15" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B16" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="53" t="s">
+      <c r="S48" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T48" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U48" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V48" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W48" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X48" s="56"/>
+    </row>
+    <row r="49" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B49" s="55"/>
+      <c r="C49" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D49" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="G49" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="55"/>
+      <c r="J49" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="K49" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="L49" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M49" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="N49" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="O49" s="56"/>
+      <c r="Q49" s="55"/>
+      <c r="R49" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="S49" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="T49" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U49" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="V49" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="W49" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X49" s="56"/>
+    </row>
+    <row r="50" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B50" s="55"/>
+      <c r="C50" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>420</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G50" s="56" t="s">
+        <v>418</v>
+      </c>
+      <c r="I50" s="55"/>
+      <c r="O50" s="56"/>
+      <c r="Q50" s="55"/>
+      <c r="X50" s="56"/>
+    </row>
+    <row r="51" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B51" s="55"/>
+      <c r="C51" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>421</v>
+      </c>
+      <c r="G51" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="I51" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="J51" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="J16" s="53" t="s">
+      <c r="K51" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="L51" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M51" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="N51" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="O51" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q51" s="55" t="s">
+        <v>317</v>
+      </c>
+      <c r="R51" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="S51" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="T51" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="U51" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="V51" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="W51" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X51" s="56" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B52" s="55"/>
+      <c r="C52" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" s="56"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="K52" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="L52" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="N52" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="O52" s="56" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q52" s="55"/>
+      <c r="R52" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="S52" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="T52" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="U52" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="V52" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="W52" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X52" s="56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B53" s="55"/>
+      <c r="C53" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F53" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" s="56" t="s">
+        <v>301</v>
+      </c>
+      <c r="I53" s="55"/>
+      <c r="J53" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="K53" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L53" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M53" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N53" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O53" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q53" s="55"/>
+      <c r="R53" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="S53" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T53" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U53" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V53" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W53" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X53" s="56" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="54" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B54" s="55"/>
+      <c r="C54" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F54" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" s="56"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="K54" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L54" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M54" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N54" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O54" s="56"/>
+      <c r="Q54" s="55"/>
+      <c r="R54" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="S54" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T54" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U54" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V54" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W54" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X54" s="56" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B55" s="55"/>
+      <c r="C55" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G55" s="56"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="K55" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L55" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M55" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N55" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O55" s="56" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q55" s="55"/>
+      <c r="R55" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="S55" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T55" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U55" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V55" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W55" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X55" s="56"/>
+    </row>
+    <row r="56" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B56" s="55"/>
+      <c r="C56" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="56"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="K56" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L56" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M56" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N56" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O56" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q56" s="55"/>
+      <c r="R56" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S56" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T56" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U56" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V56" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W56" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X56" s="56"/>
+    </row>
+    <row r="57" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B57" s="55"/>
+      <c r="C57" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G57" s="56"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="K57" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L57" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M57" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N57" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O57" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q57" s="55"/>
+      <c r="R57" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="S57" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T57" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U57" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V57" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W57" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X57" s="56"/>
+    </row>
+    <row r="58" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B58" s="55"/>
+      <c r="C58" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F58" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" s="56"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="K58" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L58" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M58" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N58" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O58" s="56" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q58" s="55"/>
+      <c r="R58" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S58" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T58" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U58" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V58" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W58" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X58" s="56"/>
+    </row>
+    <row r="59" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B59" s="55"/>
+      <c r="C59" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G59" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="I59" s="55"/>
+      <c r="J59" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K59" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L59" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M59" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N59" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O59" s="56" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q59" s="55"/>
+      <c r="R59" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="S59" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T59" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U59" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V59" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W59" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X59" s="56"/>
+    </row>
+    <row r="60" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B60" s="55"/>
+      <c r="C60" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="F60" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="G60" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="I60" s="55"/>
+      <c r="J60" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="K60" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L60" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M60" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N60" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O60" s="56" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q60" s="55"/>
+      <c r="R60" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="S60" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T60" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U60" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V60" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W60" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X60" s="56"/>
+    </row>
+    <row r="61" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B61" s="55"/>
+      <c r="C61" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="G61" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="I61" s="55"/>
+      <c r="J61" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="K61" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L61" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M61" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N61" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O61" s="56"/>
+      <c r="Q61" s="55"/>
+      <c r="R61" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="S61" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T61" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U61" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V61" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W61" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X61" s="56"/>
+    </row>
+    <row r="62" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B62" s="57"/>
+      <c r="C62" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" s="53" t="s">
+      <c r="D62" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="F62" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="G62" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="I62" s="55"/>
+      <c r="J62" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="K62" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L62" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M62" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N62" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O62" s="56"/>
+      <c r="Q62" s="55"/>
+      <c r="R62" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="S62" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T62" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U62" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V62" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W62" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X62" s="56"/>
+    </row>
+    <row r="63" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I63" s="55"/>
+      <c r="J63" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="K63" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L63" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M63" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N63" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O63" s="56"/>
+      <c r="Q63" s="55"/>
+      <c r="R63" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="S63" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T63" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U63" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V63" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W63" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X63" s="56"/>
+    </row>
+    <row r="64" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="I64" s="55"/>
+      <c r="J64" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="K64" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="L64" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M64" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="N64" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O64" s="56"/>
+      <c r="Q64" s="55"/>
+      <c r="R64" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="S64" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="T64" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="U64" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="V64" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="W64" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="X64" s="56"/>
+    </row>
+    <row r="65" spans="9:24" x14ac:dyDescent="0.2">
+      <c r="I65" s="57"/>
+      <c r="J65" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="S16" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W16" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C17" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="53" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="K17" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="L17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="S17" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="T17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="U17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V17" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W17" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C18" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C19" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="L19" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q19" s="53" t="s">
-        <v>318</v>
-      </c>
-      <c r="R19" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="S19" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="T19" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W19" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X19" s="53" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C20" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J20" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="K20" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R20" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="S20" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="T20" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W20" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X20" s="53" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C21" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="K21" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L21" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T21" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W21" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X21" s="53" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C22" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="K22" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L22" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="S22" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T22" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V22" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W22" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C23" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J23" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L23" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="S23" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T23" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V23" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W23" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C24" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L24" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R24" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="S24" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T24" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V24" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W24" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C25" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J25" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L25" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R25" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="S25" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T25" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V25" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W25" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C26" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="K26" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L26" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R26" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="S26" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T26" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V26" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W26" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C27" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J27" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="K27" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L27" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R27" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="S27" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T27" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V27" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W27" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C28" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="K28" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L28" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R28" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="S28" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T28" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V28" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W28" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C29" s="53" t="s">
+      <c r="K65" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="L65" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="M65" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="N65" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="O65" s="59"/>
+      <c r="Q65" s="57"/>
+      <c r="R65" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J29" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="K29" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L29" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R29" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="S29" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T29" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W29" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C30" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="K30" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L30" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R30" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="S30" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T30" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V30" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W30" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J31" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="K31" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L31" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M31" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N31" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R31" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="S31" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T31" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U31" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V31" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W31" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B32" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J32" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="K32" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L32" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M32" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N32" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O32" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="R32" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="S32" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T32" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U32" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V32" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W32" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C33" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="K33" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L33" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="N33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O33" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="R33" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="S33" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="T33" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="V33" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W33" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C34" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C35" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="53" t="s">
-        <v>125</v>
-      </c>
-      <c r="J35" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="K35" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="L35" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M35" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="N35" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O35" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q35" s="53" t="s">
-        <v>319</v>
-      </c>
-      <c r="R35" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="S35" s="53" t="s">
+      <c r="S65" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="T35" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U35" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="V35" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W35" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X35" s="53" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C36" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F36" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J36" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="K36" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="L36" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M36" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="N36" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O36" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="R36" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="S36" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="T36" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U36" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="V36" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W36" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X36" s="53" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C37" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J37" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="K37" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L37" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M37" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N37" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O37" s="53" t="s">
-        <v>148</v>
-      </c>
-      <c r="R37" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="S37" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T37" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U37" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V37" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W37" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X37" s="53" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C38" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F38" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J38" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="K38" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L38" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M38" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N38" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O38" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="R38" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="S38" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T38" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U38" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V38" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W38" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C39" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E39" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J39" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="K39" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L39" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M39" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N39" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O39" s="53" t="s">
-        <v>304</v>
-      </c>
-      <c r="R39" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="S39" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T39" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U39" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V39" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W39" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X39" s="53" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C40" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J40" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="K40" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L40" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M40" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N40" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O40" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="R40" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="S40" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T40" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U40" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V40" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W40" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X40" s="53" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C41" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F41" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J41" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="K41" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L41" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M41" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N41" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O41" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="R41" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="S41" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T41" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U41" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V41" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W41" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C42" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E42" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="K42" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L42" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M42" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N42" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O42" s="53" t="s">
-        <v>295</v>
-      </c>
-      <c r="R42" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="S42" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T42" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U42" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V42" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W42" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C43" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D43" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F43" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J43" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="K43" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L43" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M43" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N43" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="O43" s="53" t="s">
-        <v>296</v>
-      </c>
-      <c r="R43" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="S43" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T43" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U43" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V43" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W43" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C44" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E44" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="K44" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L44" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M44" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N44" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R44" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="S44" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T44" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U44" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V44" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W44" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C45" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E45" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J45" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="K45" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L45" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M45" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N45" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R45" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="S45" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T45" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U45" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V45" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W45" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C46" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F46" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="J46" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="K46" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L46" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M46" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N46" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R46" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="S46" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T46" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U46" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V46" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W46" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J47" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="K47" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L47" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M47" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N47" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R47" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="S47" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T47" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U47" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V47" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W47" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B48" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="C48" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E48" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F48" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="G48" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="J48" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="K48" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L48" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M48" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N48" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R48" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="S48" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T48" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U48" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V48" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W48" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C49" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="F49" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="G49" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="J49" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="K49" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="L49" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M49" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N49" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="R49" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="S49" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="T49" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U49" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="V49" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="W49" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C50" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F50" s="53" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C51" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E51" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="I51" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="J51" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="K51" s="53" t="s">
+      <c r="T65" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="U65" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="L51" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M51" s="53" t="s">
+      <c r="V65" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="N51" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="O51" s="53" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q51" s="53" t="s">
-        <v>320</v>
-      </c>
-      <c r="R51" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="S51" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="T51" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U51" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="V51" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="W51" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X51" s="53" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C52" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D52" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J52" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="K52" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="L52" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="M52" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="N52" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="O52" s="53" t="s">
-        <v>298</v>
-      </c>
-      <c r="R52" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="S52" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="T52" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="U52" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="V52" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="W52" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X52" s="53" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C53" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="53" t="s">
-        <v>303</v>
-      </c>
-      <c r="J53" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="K53" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L53" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M53" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N53" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O53" s="53" t="s">
-        <v>299</v>
-      </c>
-      <c r="R53" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="S53" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T53" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U53" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V53" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W53" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X53" s="53" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C54" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F54" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J54" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="K54" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L54" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M54" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N54" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R54" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="S54" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T54" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U54" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V54" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W54" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="X54" s="53" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C55" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="D55" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E55" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J55" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="K55" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L55" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M55" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N55" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O55" s="53" t="s">
-        <v>293</v>
-      </c>
-      <c r="R55" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="S55" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T55" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U55" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V55" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W55" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C56" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E56" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J56" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="K56" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L56" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M56" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N56" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O56" s="53" t="s">
-        <v>309</v>
-      </c>
-      <c r="R56" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="S56" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T56" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U56" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V56" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W56" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C57" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E57" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F57" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J57" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="K57" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L57" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M57" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N57" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O57" s="53" t="s">
-        <v>315</v>
-      </c>
-      <c r="R57" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="S57" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T57" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U57" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V57" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W57" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C58" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="J58" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="K58" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L58" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M58" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N58" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O58" s="53" t="s">
-        <v>300</v>
-      </c>
-      <c r="R58" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="S58" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T58" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U58" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V58" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W58" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C59" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E59" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F59" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="G59" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="J59" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="K59" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L59" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M59" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N59" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O59" s="53" t="s">
-        <v>301</v>
-      </c>
-      <c r="R59" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="S59" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T59" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U59" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V59" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W59" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C60" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="D60" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="F60" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="G60" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="J60" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="K60" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L60" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M60" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N60" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="O60" s="53" t="s">
-        <v>302</v>
-      </c>
-      <c r="R60" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="S60" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T60" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U60" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V60" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W60" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C61" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="F61" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="G61" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="J61" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="K61" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L61" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M61" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N61" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R61" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="S61" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T61" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U61" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V61" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W61" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="C62" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F62" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="G62" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="J62" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="K62" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L62" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M62" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N62" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R62" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="S62" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T62" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U62" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V62" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W62" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="J63" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="K63" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L63" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M63" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N63" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R63" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="S63" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T63" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U63" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V63" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W63" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="J64" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="K64" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L64" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M64" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N64" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R64" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="S64" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T64" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U64" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V64" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W64" s="53" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="65" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J65" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="K65" s="53" t="s">
-        <v>133</v>
-      </c>
-      <c r="L65" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="M65" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="N65" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="R65" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="S65" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="T65" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="U65" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="V65" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="W65" s="53" t="s">
-        <v>88</v>
-      </c>
+      <c r="W65" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="X65" s="59"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
